--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_41.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2518834.012065556</v>
+        <v>2511856.627373429</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979925</v>
+        <v>9956801.353979923</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979925</v>
+        <v>9956801.353979923</v>
       </c>
     </row>
     <row r="9">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -720,7 +720,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>210.6156651633976</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135.3518862151735</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>164.4576247514823</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>176.4246500889419</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>168.4149913854146</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>118.7330677017073</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>147.2737972923793</v>
+        <v>216.3725645856306</v>
       </c>
       <c r="S6" t="n">
-        <v>421</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>421</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>172.7782809922831</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>113.1819995050528</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>124.8982315818996</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>284.85671905313</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -1383,7 +1383,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H11" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1447,13 +1447,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>11.09991244551929</v>
+        <v>81.10557774904923</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>197.2737972923793</v>
@@ -1498,7 +1498,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
         <v>50.21035976018675</v>
@@ -1614,7 +1614,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G14" t="n">
         <v>53.75737228701621</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>197.2737972923793</v>
@@ -1927,19 +1927,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>284.2120239427945</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2212,7 +2212,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
-        <v>50.21035976018675</v>
+        <v>245.7617363942807</v>
       </c>
       <c r="V21" t="n">
         <v>64.51066719152016</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>259.9515598178217</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U24" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V24" t="n">
         <v>64.51066719152016</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U27" t="n">
         <v>400.2103597601867</v>
@@ -2802,7 +2802,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H29" t="n">
         <v>58.00965870352741</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2869,10 +2869,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>131.9993129555745</v>
+        <v>135.964704340989</v>
       </c>
       <c r="C32" t="n">
         <v>99.47457824299391</v>
@@ -3087,7 +3087,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X32" t="n">
         <v>242.2818334606677</v>
@@ -3109,7 +3109,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V33" t="n">
         <v>64.51066719152016</v>
@@ -3169,7 +3169,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>69.86273944538755</v>
+        <v>156.8009660958027</v>
       </c>
       <c r="Y33" t="n">
         <v>49.39139276613435</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096178</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>392.8251739264733</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3406,7 +3406,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176904</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>246.2472248460823</v>
+        <v>242.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>161.3174326828064</v>
@@ -3817,10 +3817,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3880,7 +3880,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3987,7 +3987,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H44" t="n">
         <v>58.00965870352741</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4108,16 +4108,16 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>127.1884297169626</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>49.39139276613435</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115.3301851396645</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C2" t="n">
-        <v>65.35586368209485</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D2" t="n">
-        <v>54.91227202568093</v>
+        <v>206.5094030182917</v>
       </c>
       <c r="E2" t="n">
-        <v>50.50490878641967</v>
+        <v>202.1020397790304</v>
       </c>
       <c r="F2" t="n">
-        <v>45.565889889438</v>
+        <v>197.1630208820488</v>
       </c>
       <c r="G2" t="n">
-        <v>41.77056434699738</v>
+        <v>193.3676953396081</v>
       </c>
       <c r="H2" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I2" t="n">
         <v>33.68</v>
@@ -4330,13 +4330,13 @@
         <v>33.68</v>
       </c>
       <c r="M2" t="n">
-        <v>433.6300000000001</v>
+        <v>33.68</v>
       </c>
       <c r="N2" t="n">
-        <v>850.4200000000001</v>
+        <v>450.47</v>
       </c>
       <c r="O2" t="n">
-        <v>1267.21</v>
+        <v>867.26</v>
       </c>
       <c r="P2" t="n">
         <v>1267.21</v>
@@ -4345,28 +4345,28 @@
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>310.5996251784331</v>
+        <v>462.1967561710438</v>
       </c>
       <c r="Y2" t="n">
-        <v>198.1577739836791</v>
+        <v>349.7549049762899</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>588.5229020987573</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C3" t="n">
-        <v>588.5229020987573</v>
+        <v>535.3221332706096</v>
       </c>
       <c r="D3" t="n">
-        <v>588.5229020987573</v>
+        <v>535.3221332706096</v>
       </c>
       <c r="E3" t="n">
-        <v>588.5229020987573</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>588.5229020987573</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>588.5229020987573</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="H3" t="n">
-        <v>252.9995817084329</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4421,31 +4421,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>865.523468466658</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>798.2871048660405</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T3" t="n">
-        <v>792.8752208079458</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>792.6627362016965</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V3" t="n">
-        <v>778.0054966143024</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W3" t="n">
-        <v>745.3053522609403</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>725.2419790837811</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y3" t="n">
-        <v>725.2419790837811</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>815.6346286497526</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="C4" t="n">
-        <v>941.6366344681884</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="D4" t="n">
-        <v>941.6366344681884</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="E4" t="n">
-        <v>1059.042529832437</v>
+        <v>625.7549448492859</v>
       </c>
       <c r="F4" t="n">
-        <v>1183.403502424373</v>
+        <v>750.1159174412214</v>
       </c>
       <c r="G4" t="n">
-        <v>1183.403502424373</v>
+        <v>903.5224833281067</v>
       </c>
       <c r="H4" t="n">
-        <v>1183.403502424373</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="I4" t="n">
-        <v>1183.403502424373</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>221.7556791588049</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>221.7556791588049</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="V4" t="n">
-        <v>420.5770720447508</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="W4" t="n">
-        <v>592.4679903044282</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="X4" t="n">
-        <v>592.4679903044282</v>
+        <v>507.9260406378729</v>
       </c>
       <c r="Y4" t="n">
-        <v>703.8772909834605</v>
+        <v>507.9260406378729</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H5" t="n">
         <v>33.68</v>
@@ -4564,46 +4564,46 @@
         <v>33.68</v>
       </c>
       <c r="L5" t="n">
-        <v>450.47</v>
+        <v>33.68</v>
       </c>
       <c r="M5" t="n">
-        <v>867.26</v>
+        <v>33.68</v>
       </c>
       <c r="N5" t="n">
-        <v>867.26</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1284.05</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1684</v>
+        <v>1267.21</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
       </c>
       <c r="R5" t="n">
-        <v>1684</v>
+        <v>1513.88384708544</v>
       </c>
       <c r="S5" t="n">
-        <v>1588.193769896644</v>
+        <v>1418.077616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1399.632576231427</v>
+        <v>1229.516423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V5" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W5" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="C6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="D6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="E6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="F6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="G6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="H6" t="n">
-        <v>153.6123916178862</v>
+        <v>33.68</v>
       </c>
       <c r="I6" t="n">
         <v>33.68</v>
@@ -4661,28 +4661,28 @@
         <v>1189.112420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1040.351008962092</v>
+        <v>970.554274322444</v>
       </c>
       <c r="S6" t="n">
-        <v>615.0984837095665</v>
+        <v>903.3179107218266</v>
       </c>
       <c r="T6" t="n">
-        <v>609.6865996514717</v>
+        <v>897.9060266637318</v>
       </c>
       <c r="U6" t="n">
-        <v>609.4741150452224</v>
+        <v>897.6935420574825</v>
       </c>
       <c r="V6" t="n">
-        <v>594.8168754578284</v>
+        <v>883.0363024700885</v>
       </c>
       <c r="W6" t="n">
-        <v>562.1167311044662</v>
+        <v>457.7837772175632</v>
       </c>
       <c r="X6" t="n">
-        <v>542.053357927307</v>
+        <v>33.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>542.053357927307</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>667.3336316425992</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="C7" t="n">
-        <v>793.335637461035</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="D7" t="n">
-        <v>906.6547815860351</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="E7" t="n">
-        <v>1024.483685797448</v>
+        <v>765.7058065656541</v>
       </c>
       <c r="F7" t="n">
-        <v>1024.483685797448</v>
+        <v>890.0667791575896</v>
       </c>
       <c r="G7" t="n">
-        <v>1024.483685797448</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.483685797448</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I7" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J7" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4746,22 +4746,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>70.93025509417312</v>
+        <v>202.5043168300085</v>
       </c>
       <c r="U7" t="n">
-        <v>317.4814477324597</v>
+        <v>449.0555094682952</v>
       </c>
       <c r="V7" t="n">
-        <v>516.3028406184058</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="W7" t="n">
-        <v>516.3028406184058</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="X7" t="n">
-        <v>667.3336316425992</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="Y7" t="n">
-        <v>667.3336316425992</v>
+        <v>647.8769023542411</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>285.4463380542246</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C8" t="n">
-        <v>235.472016596655</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D8" t="n">
-        <v>225.028424940241</v>
+        <v>206.5094030182917</v>
       </c>
       <c r="E8" t="n">
-        <v>50.50490878641967</v>
+        <v>202.1020397790304</v>
       </c>
       <c r="F8" t="n">
-        <v>45.565889889438</v>
+        <v>197.1630208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>41.77056434699738</v>
+        <v>193.3676953396081</v>
       </c>
       <c r="H8" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I8" t="n">
         <v>33.68</v>
@@ -4810,10 +4810,10 @@
         <v>1258.569113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1675.359113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1675.359113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4822,25 +4822,25 @@
         <v>1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1588.193769896644</v>
+        <v>1569.674747974694</v>
       </c>
       <c r="T8" t="n">
-        <v>1399.632576231427</v>
+        <v>1381.113554309478</v>
       </c>
       <c r="U8" t="n">
-        <v>1147.893892848992</v>
+        <v>1129.374870927043</v>
       </c>
       <c r="V8" t="n">
-        <v>915.7211411653319</v>
+        <v>897.2021192433824</v>
       </c>
       <c r="W8" t="n">
-        <v>674.9398522956878</v>
+        <v>656.4208303737385</v>
       </c>
       <c r="X8" t="n">
-        <v>480.7157780929932</v>
+        <v>462.1967561710438</v>
       </c>
       <c r="Y8" t="n">
-        <v>368.2739268982392</v>
+        <v>349.7549049762899</v>
       </c>
     </row>
     <row r="9">
@@ -4895,28 +4895,28 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>865.523468466658</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>798.2871048660405</v>
+        <v>914.1911790813851</v>
       </c>
       <c r="T9" t="n">
-        <v>388.8348167675417</v>
+        <v>908.7792950232904</v>
       </c>
       <c r="U9" t="n">
-        <v>101.1007571179154</v>
+        <v>908.5668104170411</v>
       </c>
       <c r="V9" t="n">
-        <v>86.44351753052129</v>
+        <v>489.8691667892429</v>
       </c>
       <c r="W9" t="n">
-        <v>53.74337317715914</v>
+        <v>457.1690224358807</v>
       </c>
       <c r="X9" t="n">
-        <v>33.68</v>
+        <v>437.1056492587216</v>
       </c>
       <c r="Y9" t="n">
         <v>33.68</v>
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370.4152349320102</v>
+        <v>606.6988222554638</v>
       </c>
       <c r="C10" t="n">
-        <v>370.4152349320102</v>
+        <v>606.6988222554638</v>
       </c>
       <c r="D10" t="n">
-        <v>440.1997275886753</v>
+        <v>720.0179663804639</v>
       </c>
       <c r="E10" t="n">
-        <v>558.0286318000883</v>
+        <v>720.0179663804639</v>
       </c>
       <c r="F10" t="n">
-        <v>682.3896043920238</v>
+        <v>844.3789389723994</v>
       </c>
       <c r="G10" t="n">
-        <v>682.3896043920238</v>
+        <v>997.7855048592846</v>
       </c>
       <c r="H10" t="n">
-        <v>851.9061895514213</v>
+        <v>1167.302090018682</v>
       </c>
       <c r="I10" t="n">
-        <v>1073.039068487504</v>
+        <v>1388.434968954765</v>
       </c>
       <c r="J10" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T10" t="n">
-        <v>259.005934252978</v>
+        <v>33.68</v>
       </c>
       <c r="U10" t="n">
-        <v>259.005934252978</v>
+        <v>33.68</v>
       </c>
       <c r="V10" t="n">
-        <v>259.005934252978</v>
+        <v>232.501392885946</v>
       </c>
       <c r="W10" t="n">
-        <v>259.005934252978</v>
+        <v>232.501392885946</v>
       </c>
       <c r="X10" t="n">
-        <v>259.005934252978</v>
+        <v>383.5321839101395</v>
       </c>
       <c r="Y10" t="n">
-        <v>370.4152349320102</v>
+        <v>494.9414845891717</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
         <v>44.72</v>
@@ -5035,16 +5035,16 @@
         <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L11" t="n">
-        <v>179.7320762183977</v>
+        <v>598.13</v>
       </c>
       <c r="M11" t="n">
-        <v>690.5809049473327</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N11" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O11" t="n">
         <v>1797.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E12" t="n">
         <v>44.72</v>
@@ -5132,31 +5132,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>937.5750872192207</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>819.8336731135527</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5257,13 +5257,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5275,13 +5275,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N14" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O14" t="n">
         <v>1797.400904947332</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.9618669904511</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F15" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H15" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I15" t="n">
         <v>44.72</v>
@@ -5369,31 +5369,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1112.336029812561</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>913.0695679010663</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>795.3281537953983</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>739.4112192322531</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>688.6936841209533</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V15" t="n">
-        <v>623.5313940285087</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>540.3261991700961</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X15" t="n">
-        <v>469.7577754878864</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>419.8674797645184</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5457,10 +5457,10 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V16" t="n">
         <v>521.9574820108303</v>
@@ -5509,22 +5509,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
         <v>989.4391130376558</v>
       </c>
       <c r="M17" t="n">
-        <v>989.4391130376558</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N17" t="n">
-        <v>1542.849113037656</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1508.625837177891</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>1497.413804404639</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>1497.413804404639</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>1497.413804404639</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F18" t="n">
-        <v>1497.413804404639</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>1497.413804404639</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>1299.887161339897</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="J18" t="n">
-        <v>1204.524099806763</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K18" t="n">
-        <v>1393.716915901147</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L18" t="n">
-        <v>1665.067377496347</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M18" t="n">
-        <v>1751.147919239206</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N18" t="n">
-        <v>1884.428203846775</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2123.470655530493</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2036.733538088506</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>1918.992123982838</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T18" t="n">
-        <v>1863.075189419693</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U18" t="n">
-        <v>1812.357654308393</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V18" t="n">
-        <v>1747.195364215948</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>1663.990169357536</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>1593.421745675326</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>1543.531449951958</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1184.48476868153</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C19" t="n">
-        <v>1260.986774499966</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D19" t="n">
-        <v>1324.805918624966</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1393.134822836379</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1467.995795428314</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1571.9023613152</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H19" t="n">
-        <v>1691.918946474597</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1863.55182541068</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>2175.135566063132</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K19" t="n">
-        <v>2236</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>2161.709466507294</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M19" t="n">
-        <v>1989.354303474415</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1765.935035523218</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1472.555677867648</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>1131.699215919893</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>752.0635932677734</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>371.6574033878228</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>359.1589390415042</v>
+        <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>497.7346182003091</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>694.7858108385957</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>844.1072037245417</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W19" t="n">
-        <v>966.4981219842191</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X19" t="n">
-        <v>1060.318130336206</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y19" t="n">
-        <v>1122.227431015238</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="20">
@@ -5746,19 +5746,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>1682.59</v>
       </c>
       <c r="N20" t="n">
-        <v>1129.18</v>
+        <v>2236</v>
       </c>
       <c r="O20" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P20" t="n">
         <v>2236</v>
@@ -5767,7 +5767,7 @@
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
         <v>2085.68327354774</v>
@@ -5798,25 +5798,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.9618669904511</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C21" t="n">
-        <v>373.7498342171993</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D21" t="n">
-        <v>373.7498342171993</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E21" t="n">
-        <v>373.7498342171993</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F21" t="n">
-        <v>373.7498342171993</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H21" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I21" t="n">
         <v>44.72</v>
@@ -5846,28 +5846,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>913.0695679010663</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>795.3281537953983</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>739.4112192322531</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>688.6936841209533</v>
+        <v>578.9834316121869</v>
       </c>
       <c r="V21" t="n">
-        <v>623.5313940285087</v>
+        <v>513.8211415197422</v>
       </c>
       <c r="W21" t="n">
-        <v>540.3261991700961</v>
+        <v>430.6159466613296</v>
       </c>
       <c r="X21" t="n">
-        <v>469.7577754878864</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y21" t="n">
-        <v>419.8674797645184</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="22">
@@ -5877,16 +5877,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C22" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D22" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E22" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F22" t="n">
         <v>1153.55685638681</v>
@@ -5931,22 +5931,22 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X22" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y22" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="23">
@@ -5980,19 +5980,19 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L23" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M23" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N23" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O23" t="n">
         <v>1243.990904947333</v>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55.93203277325181</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>937.5750872192207</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>819.8336731135527</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>763.9167385504074</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U24" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V24" t="n">
-        <v>294.5015598113094</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W24" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X24" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="25">
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
         <v>946.5478354584615</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6217,31 +6217,31 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L26" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M26" t="n">
-        <v>946.8779417665908</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>946.8779417665908</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O26" t="n">
-        <v>1500.287941766591</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
         <v>2085.68327354774</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="I27" t="n">
         <v>44.72</v>
@@ -6326,22 +6326,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504074</v>
       </c>
       <c r="U27" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V27" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>274.6072361907175</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
         <v>103.3156148520479</v>
@@ -6457,49 +6457,49 @@
         <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>598.13</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="L29" t="n">
-        <v>1151.54</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M29" t="n">
-        <v>1662.388828728935</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N29" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O29" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P29" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
       </c>
       <c r="R29" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S29" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.2429040110725</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S30" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T30" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U30" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V30" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W30" t="n">
-        <v>274.6072361907174</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X30" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.1485167851397</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="31">
@@ -6694,22 +6694,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M32" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N32" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6730,13 +6730,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.2429040110725</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C33" t="n">
-        <v>108.0308712378207</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G33" t="n">
         <v>44.72</v>
@@ -6803,19 +6803,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>204.0388125085078</v>
+        <v>469.7577754878864</v>
       </c>
       <c r="Y33" t="n">
-        <v>154.1485167851398</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="34">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>1151.54</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1151.54</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N35" t="n">
-        <v>1151.54</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>1704.95</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>275.2516144816847</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>803.3593153922999</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>685.6179012866319</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>629.7009667234867</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>360.0475229791199</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y36" t="n">
-        <v>310.1572272557519</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="37">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,46 +7141,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>690.5809049473327</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M38" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N38" t="n">
-        <v>690.5809049473327</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7192,25 +7192,25 @@
         <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851398</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="40">
@@ -7353,7 +7353,7 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
         <v>372.6360891248843</v>
@@ -7378,34 +7378,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L41" t="n">
         <v>733.1420762183976</v>
@@ -7444,10 +7444,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7536,25 +7536,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
         <v>1549.112886369176</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
         <v>103.3156148520479</v>
@@ -7645,16 +7645,16 @@
         <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>1129.18</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>1129.18</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P44" t="n">
         <v>2236</v>
@@ -7663,28 +7663,28 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F45" t="n">
         <v>44.72</v>
@@ -7751,19 +7751,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H46" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
         <v>1860.696627021627</v>
@@ -7839,10 +7839,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>948.2520266322164</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>898.2489580698352</v>
@@ -7982,7 +7982,7 @@
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>404.2769590305805</v>
       </c>
       <c r="Q2" t="n">
         <v>593.8226843274854</v>
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>965.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>881.2388570597343</v>
       </c>
       <c r="O5" t="n">
         <v>491.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>404.2769590305805</v>
+        <v>421.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8453,13 +8453,13 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>491.2478695740924</v>
+        <v>78.97603822292498</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>181.5508529763179</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,10 +8678,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>206.6237041381302</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8918,16 +8918,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>629.2478695740924</v>
+        <v>327.370891705079</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>327.370891705079</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,22 +9389,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>661.3924512348954</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
         <v>172.8226843274854</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,10 +9635,10 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>570.6337105418884</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>559.2870600406815</v>
@@ -9860,10 +9860,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,16 +9872,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
+        <v>93.38475247205329</v>
+      </c>
+      <c r="L29" t="n">
         <v>559</v>
       </c>
-      <c r="L29" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
-        <v>497.6541815759616</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
         <v>70.24786957409245</v>
@@ -10118,7 +10118,7 @@
         <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>801.385149773304</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>211.4002806471676</v>
       </c>
       <c r="P32" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N35" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>536.7012014548227</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11288,19 +11288,19 @@
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>141.1524110730752</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789646</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>517090.1070984007</v>
+        <v>515527.4940049556</v>
       </c>
       <c r="C6" t="n">
-        <v>667314.6228619451</v>
+        <v>665752.0097685003</v>
       </c>
       <c r="D6" t="n">
-        <v>669349.8958599841</v>
+        <v>667787.2827665393</v>
       </c>
       <c r="E6" t="n">
-        <v>355780.063114375</v>
+        <v>354038.2133012674</v>
       </c>
       <c r="F6" t="n">
-        <v>686298.9584598794</v>
+        <v>684557.1086467713</v>
       </c>
       <c r="G6" t="n">
-        <v>688244.5349280642</v>
+        <v>686502.685114957</v>
       </c>
       <c r="H6" t="n">
-        <v>690192.811745366</v>
+        <v>688450.9619322583</v>
       </c>
       <c r="I6" t="n">
-        <v>692143.8083887264</v>
+        <v>690401.9585756183</v>
       </c>
       <c r="J6" t="n">
-        <v>265905.5445903513</v>
+        <v>264163.6947772434</v>
       </c>
       <c r="K6" t="n">
-        <v>696054.0403425702</v>
+        <v>694312.1905294631</v>
       </c>
       <c r="L6" t="n">
-        <v>698013.31590283</v>
+        <v>696271.4660897225</v>
       </c>
       <c r="M6" t="n">
-        <v>651399.3917988092</v>
+        <v>649657.5419857015</v>
       </c>
       <c r="N6" t="n">
-        <v>701940.2888336624</v>
+        <v>700198.4390205552</v>
       </c>
       <c r="O6" t="n">
-        <v>423908.0280914006</v>
+        <v>422166.1782782932</v>
       </c>
       <c r="P6" t="n">
-        <v>705878.6309424109</v>
+        <v>704136.781129303</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -26999,7 +26999,7 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
@@ -27024,10 +27024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -27091,13 +27091,13 @@
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
@@ -27115,7 +27115,7 @@
         <v>-0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27499,7 +27499,7 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="Y2" t="n">
         <v>400</v>
@@ -27512,16 +27512,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>249.2046704311531</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>178.2144724704303</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27533,7 +27533,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27591,25 +27591,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>399.5727183361977</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>176.6334556201183</v>
@@ -27618,7 +27618,7 @@
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>201.5631523845074</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>82.46360744287983</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>98.39331818964122</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
+        <v>330.9012327067487</v>
+      </c>
+      <c r="S6" t="n">
         <v>400</v>
-      </c>
-      <c r="S6" t="n">
-        <v>45.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>11.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27831,31 +27831,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>337.1585229200421</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K7" t="n">
         <v>400</v>
-      </c>
-      <c r="K7" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>342.9276591687177</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28031,22 +28031,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
+        <v>341.6657683827117</v>
+      </c>
+      <c r="T9" t="n">
         <v>400</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
-        <v>115.3536407070567</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -28065,22 +28065,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>356.0256045774394</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
@@ -28089,10 +28089,10 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>192.8975085551589</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28162,7 +28162,7 @@
         <v>350</v>
       </c>
       <c r="H11" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I11" t="n">
         <v>150.0811596826846</v>
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28226,13 +28226,13 @@
         <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>350</v>
@@ -28277,7 +28277,7 @@
         <v>350</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U12" t="n">
         <v>350</v>
@@ -28393,7 +28393,7 @@
         <v>350</v>
       </c>
       <c r="F14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G14" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28475,13 +28475,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>86.14103844006436</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>350</v>
@@ -28593,13 +28593,13 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
+        <v>350</v>
+      </c>
+      <c r="U16" t="n">
+        <v>350</v>
+      </c>
+      <c r="V16" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U16" t="n">
-        <v>350</v>
-      </c>
-      <c r="V16" t="n">
-        <v>350</v>
       </c>
       <c r="W16" t="n">
         <v>350</v>
@@ -28706,19 +28706,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>136.6167105523272</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28836,13 +28836,13 @@
         <v>350</v>
       </c>
       <c r="V19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="W19" t="n">
         <v>350</v>
       </c>
       <c r="X19" t="n">
-        <v>342.2113306341345</v>
+        <v>350</v>
       </c>
       <c r="Y19" t="n">
         <v>350</v>
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28949,13 +28949,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28982,7 +28982,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -28991,7 +28991,7 @@
         <v>350</v>
       </c>
       <c r="U21" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="V21" t="n">
         <v>350</v>
@@ -29025,7 +29025,7 @@
         <v>350</v>
       </c>
       <c r="F22" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G22" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29219,16 +29219,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -29253,58 +29253,58 @@
         <v>350</v>
       </c>
       <c r="C25" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" t="n">
+        <v>350</v>
+      </c>
+      <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="n">
+        <v>350</v>
+      </c>
+      <c r="H25" t="n">
+        <v>350</v>
+      </c>
+      <c r="I25" t="n">
+        <v>350</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="n">
+        <v>350</v>
+      </c>
+      <c r="L25" t="n">
+        <v>350</v>
+      </c>
+      <c r="M25" t="n">
+        <v>350</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350</v>
+      </c>
+      <c r="O25" t="n">
+        <v>350</v>
+      </c>
+      <c r="P25" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>350</v>
+      </c>
+      <c r="S25" t="n">
+        <v>350</v>
+      </c>
+      <c r="T25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="D25" t="n">
-        <v>350</v>
-      </c>
-      <c r="E25" t="n">
-        <v>350</v>
-      </c>
-      <c r="F25" t="n">
-        <v>350</v>
-      </c>
-      <c r="G25" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" t="n">
-        <v>350</v>
-      </c>
-      <c r="I25" t="n">
-        <v>350</v>
-      </c>
-      <c r="J25" t="n">
-        <v>350</v>
-      </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
-      <c r="L25" t="n">
-        <v>350</v>
-      </c>
-      <c r="M25" t="n">
-        <v>350</v>
-      </c>
-      <c r="N25" t="n">
-        <v>350</v>
-      </c>
-      <c r="O25" t="n">
-        <v>350</v>
-      </c>
-      <c r="P25" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>350</v>
-      </c>
-      <c r="R25" t="n">
-        <v>350</v>
-      </c>
-      <c r="S25" t="n">
-        <v>350</v>
-      </c>
-      <c r="T25" t="n">
-        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29429,7 +29429,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
-        <v>154.448623365906</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29462,7 +29462,7 @@
         <v>350</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>287.3222374745577</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -29581,7 +29581,7 @@
         <v>350</v>
       </c>
       <c r="G29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H29" t="n">
         <v>350</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29648,10 +29648,10 @@
         <v>350</v>
       </c>
       <c r="C30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29693,7 +29693,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="C32" t="n">
         <v>350</v>
@@ -29866,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="W32" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29888,7 +29888,7 @@
         <v>350</v>
       </c>
       <c r="D33" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -29897,7 +29897,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>332.1680871864211</v>
@@ -29939,7 +29939,7 @@
         <v>350</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V33" t="n">
         <v>350</v>
@@ -29948,7 +29948,7 @@
         <v>350</v>
       </c>
       <c r="X33" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="Y33" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30140,7 +30140,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30185,7 +30185,7 @@
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40">
@@ -30489,10 +30489,10 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
+        <v>350</v>
+      </c>
+      <c r="U40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U40" t="n">
-        <v>350</v>
       </c>
       <c r="V40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30580,7 +30580,7 @@
         <v>350</v>
       </c>
       <c r="X41" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="Y41" t="n">
         <v>350</v>
@@ -30596,10 +30596,10 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30659,7 +30659,7 @@
         <v>350</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30693,40 +30693,40 @@
         <v>350</v>
       </c>
       <c r="I43" t="n">
+        <v>350</v>
+      </c>
+      <c r="J43" t="n">
+        <v>350</v>
+      </c>
+      <c r="K43" t="n">
+        <v>350</v>
+      </c>
+      <c r="L43" t="n">
+        <v>350</v>
+      </c>
+      <c r="M43" t="n">
+        <v>350</v>
+      </c>
+      <c r="N43" t="n">
+        <v>350</v>
+      </c>
+      <c r="O43" t="n">
+        <v>350</v>
+      </c>
+      <c r="P43" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>350</v>
+      </c>
+      <c r="R43" t="n">
+        <v>350</v>
+      </c>
+      <c r="S43" t="n">
+        <v>350</v>
+      </c>
+      <c r="T43" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="J43" t="n">
-        <v>350</v>
-      </c>
-      <c r="K43" t="n">
-        <v>350</v>
-      </c>
-      <c r="L43" t="n">
-        <v>350</v>
-      </c>
-      <c r="M43" t="n">
-        <v>350</v>
-      </c>
-      <c r="N43" t="n">
-        <v>350</v>
-      </c>
-      <c r="O43" t="n">
-        <v>350</v>
-      </c>
-      <c r="P43" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>350</v>
-      </c>
-      <c r="R43" t="n">
-        <v>350</v>
-      </c>
-      <c r="S43" t="n">
-        <v>350</v>
-      </c>
-      <c r="T43" t="n">
-        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30766,7 +30766,7 @@
         <v>350</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H44" t="n">
         <v>350</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30842,7 +30842,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30887,16 +30887,16 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
       </c>
       <c r="X45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>350</v>
@@ -30933,49 +30933,49 @@
         <v>350</v>
       </c>
       <c r="J46" t="n">
+        <v>350</v>
+      </c>
+      <c r="K46" t="n">
+        <v>350</v>
+      </c>
+      <c r="L46" t="n">
+        <v>350</v>
+      </c>
+      <c r="M46" t="n">
+        <v>350</v>
+      </c>
+      <c r="N46" t="n">
+        <v>350</v>
+      </c>
+      <c r="O46" t="n">
+        <v>350</v>
+      </c>
+      <c r="P46" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>350</v>
+      </c>
+      <c r="S46" t="n">
+        <v>350</v>
+      </c>
+      <c r="T46" t="n">
+        <v>350</v>
+      </c>
+      <c r="U46" t="n">
+        <v>350</v>
+      </c>
+      <c r="V46" t="n">
+        <v>350</v>
+      </c>
+      <c r="W46" t="n">
+        <v>350</v>
+      </c>
+      <c r="X46" t="n">
         <v>342.2113306341341</v>
-      </c>
-      <c r="K46" t="n">
-        <v>350</v>
-      </c>
-      <c r="L46" t="n">
-        <v>350</v>
-      </c>
-      <c r="M46" t="n">
-        <v>350</v>
-      </c>
-      <c r="N46" t="n">
-        <v>350</v>
-      </c>
-      <c r="O46" t="n">
-        <v>350</v>
-      </c>
-      <c r="P46" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>350</v>
-      </c>
-      <c r="R46" t="n">
-        <v>350</v>
-      </c>
-      <c r="S46" t="n">
-        <v>350</v>
-      </c>
-      <c r="T46" t="n">
-        <v>350</v>
-      </c>
-      <c r="U46" t="n">
-        <v>350</v>
-      </c>
-      <c r="V46" t="n">
-        <v>350</v>
-      </c>
-      <c r="W46" t="n">
-        <v>350</v>
-      </c>
-      <c r="X46" t="n">
-        <v>350</v>
       </c>
       <c r="Y46" t="n">
         <v>350</v>
@@ -34752,7 +34752,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>421</v>
@@ -34761,7 +34761,7 @@
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>403.989898989899</v>
       </c>
       <c r="Q2" t="n">
         <v>421</v>
@@ -34877,25 +34877,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>118.5918134992412</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34904,7 +34904,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>2.392842168291226</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34986,22 +34986,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>403.989898989899</v>
       </c>
       <c r="O5" t="n">
         <v>421</v>
       </c>
       <c r="P5" t="n">
-        <v>403.989898989899</v>
+        <v>421</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,31 +35117,31 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>160.5250672999238</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>132.90309266246</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35232,13 +35232,13 @@
         <v>421</v>
       </c>
       <c r="O8" t="n">
+        <v>8.728168648832536</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>421</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.728168648832536</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,22 +35351,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>70.4893865218839</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
@@ -35375,10 +35375,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>157.6285597192511</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,10 +35457,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35697,16 +35697,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35879,13 +35879,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V16" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W16" t="n">
         <v>123.6271901612903</v>
@@ -35931,25 +35931,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>257.1230221309866</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36122,13 +36122,13 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W19" t="n">
         <v>123.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>94.76768520402692</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y19" t="n">
         <v>62.53464715053764</v>
@@ -36168,22 +36168,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36311,7 +36311,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F22" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G22" t="n">
         <v>104.95612715847</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36402,22 +36402,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
+        <v>257.1230221309868</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>559</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>93.38475247205321</v>
-      </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>559</v>
@@ -36539,7 +36539,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>69.48608398608951</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D25" t="n">
         <v>64.46378194444452</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36639,10 +36639,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36651,16 +36651,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O26" t="n">
         <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>93.38475247205329</v>
+      </c>
+      <c r="L29" t="n">
         <v>559</v>
       </c>
-      <c r="L29" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>20.40522350612631</v>
+        <v>559</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>559</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,25 +37116,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="P32" t="n">
         <v>559</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>536.4141414141411</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>300.1141042229715</v>
+      </c>
+      <c r="M38" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N38" t="n">
         <v>559</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37775,10 +37775,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596762</v>
       </c>
       <c r="V40" t="n">
         <v>150.8296897837838</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37979,7 +37979,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I43" t="n">
-        <v>165.577875014016</v>
+        <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
         <v>314.7310511640923</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38067,19 +38067,19 @@
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>141.1524110730752</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
@@ -38261,7 +38261,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y46" t="n">
         <v>62.53464715053764</v>
